--- a/docs/data/predictions/2026-04-26_ST.xlsx
+++ b/docs/data/predictions/2026-04-26_ST.xlsx
@@ -541,12 +541,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -558,8 +562,10 @@
           <t>PRESTIGE HALL</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>6</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -576,47 +582,79 @@
           <t>6/2/2/2/6/4</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4.857142857142858</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.6964</v>
-      </c>
-      <c r="R2" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.6</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4.857142857142858</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5.6964</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -628,8 +666,10 @@
           <t>THE HEIR</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>5</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -646,47 +686,79 @@
           <t>3/2/3/3/8/4</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>6.142857142857143</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.6282</v>
-      </c>
-      <c r="R3" t="n">
-        <v>12</v>
-      </c>
-      <c r="S3" t="n">
-        <v>7.1</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6.142857142857143</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5.6282</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -698,8 +770,10 @@
           <t>LUCRATIVE EIGHT</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -716,47 +790,79 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4.857142857142858</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.3184</v>
-      </c>
-      <c r="R4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S4" t="n">
-        <v>9.699999999999999</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4.857142857142858</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5.3184</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -768,8 +874,10 @@
           <t>MATZDEN</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>2</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -786,47 +894,79 @@
           <t>6/12/5/6</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>10</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.2892</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9.9</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.2892</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -838,8 +978,10 @@
           <t>TURIN CHAMPIONS</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>4</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -856,47 +998,79 @@
           <t>9/-/1/2/2/6</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>10</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6.0627</v>
-      </c>
-      <c r="R6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6.62</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>6.0627</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -908,8 +1082,10 @@
           <t>BIG RETURN</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>3</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -926,47 +1102,79 @@
           <t>1/4/3/4/5/9</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>5.736842105263158</v>
-      </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.3576</v>
-      </c>
-      <c r="R7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8.199999999999999</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5.736842105263158</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5.3576</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -978,8 +1186,10 @@
           <t>AMAZING AWARD</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>5</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -996,47 +1206,79 @@
           <t>4/4/2/7/7/4</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5.263157894736842</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.2978</v>
-      </c>
-      <c r="R8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8.699999999999999</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5.263157894736842</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5.2978</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1048,8 +1290,10 @@
           <t>MASSIVE GLORY</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>10</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1066,47 +1310,79 @@
           <t>6</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>6.210526315789473</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.2556</v>
-      </c>
-      <c r="R9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>9</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6.210526315789473</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5.2556</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1118,8 +1394,10 @@
           <t>MR INCREDIBLE</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1136,47 +1414,79 @@
           <t>6/1</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.4932</v>
-      </c>
-      <c r="R10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.8</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>6.4932</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1188,8 +1498,10 @@
           <t>ABSOLUTE HEART</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1206,47 +1518,79 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>10</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.6784</v>
-      </c>
-      <c r="R11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" t="n">
-        <v>8.5</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5.6784</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1258,8 +1602,10 @@
           <t>GOLDENTRONICMIGHTY</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>10</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1276,47 +1622,79 @@
           <t>12/5/6/11/4/2</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.3921</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>11.3</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5.3921</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1328,8 +1706,10 @@
           <t>MASSIVE REWARD</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>4</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1346,47 +1726,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.2416</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>13.1</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5.2416</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1398,8 +1810,10 @@
           <t>NYX GLUCK</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>7</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,47 +1830,79 @@
           <t>4/10/4/3/5/1</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6.785714285714286</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5.8468</v>
-      </c>
-      <c r="R14" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>6.7</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6.81</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>6.785714285714286</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5.8468</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1468,8 +1914,10 @@
           <t>ROBOT STAR</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>10</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1486,47 +1934,79 @@
           <t>2/5/2/1/8/4</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>9.357142857142858</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.8371</v>
-      </c>
-      <c r="R15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6.8</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>9.357142857142858</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5.8371</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1538,8 +2018,10 @@
           <t>POET'S REIGN</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1556,47 +2038,79 @@
           <t>11/2</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6.142857142857143</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.7808</v>
-      </c>
-      <c r="R16" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>7.2</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6.33</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6.142857142857143</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5.7808</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>4</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1608,8 +2122,10 @@
           <t>WARRIORS DREAM</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>11</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1626,47 +2142,79 @@
           <t>5/1/6/3/5/5</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.439</v>
-      </c>
-      <c r="R17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10.1</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5.439</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1678,8 +2226,10 @@
           <t>KA YING RISING</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1696,47 +2246,79 @@
           <t>1/1/1/1/1/1</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>10</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7.0784</v>
-      </c>
-      <c r="R18" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.2</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>7.0784</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1748,8 +2330,10 @@
           <t>FAST NETWORK</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1766,47 +2350,79 @@
           <t>5/1/3/3/2/6</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.0796</v>
-      </c>
-      <c r="R19" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.9</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>6.0796</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1818,8 +2434,10 @@
           <t>HELIOS EXPRESS</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1836,47 +2454,79 @@
           <t>2/2/2/5/3/5</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="K20" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.0012</v>
-      </c>
-      <c r="R20" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6.4</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6.0012</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1888,8 +2538,10 @@
           <t>RAGING BLIZZARD</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1906,47 +2558,79 @@
           <t>3/5/4/2/5/2</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="K21" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.9946</v>
-      </c>
-      <c r="R21" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6.5</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5.9946</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1958,8 +2642,10 @@
           <t>COOL BOY</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>13</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1976,47 +2662,79 @@
           <t>4/1/1/1/3</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>7</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.3938</v>
-      </c>
-      <c r="R22" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.3</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>9.07</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6.3938</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2028,8 +2746,10 @@
           <t>GENEVA</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>9</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2046,47 +2766,79 @@
           <t>2/3/5/6/1/2</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.0984</v>
-      </c>
-      <c r="R23" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.8</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7.62</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6.0984</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>3</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2098,8 +2850,10 @@
           <t>LIFELINE EXPRESS</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>2</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2116,47 +2870,79 @@
           <t>6/2/3/3/4/9</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="K24" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>7</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.642</v>
-      </c>
-      <c r="R24" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="S24" t="n">
-        <v>9.1</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5.642</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2168,8 +2954,10 @@
           <t>CELESTIAL HERO</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>4</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2186,47 +2974,79 @@
           <t>8/4/4/3/6/6</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="K25" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.4733</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10.9</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5.4733</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>7</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2238,8 +3058,10 @@
           <t>INVINCIBLE IBIS</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2256,47 +3078,79 @@
           <t>1/2/6/1/1/1</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="K26" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>7.4125</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.5278</v>
-      </c>
-      <c r="R26" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.9</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>7.4125</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6.5278</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2308,8 +3162,10 @@
           <t>LITTLE PARADISE</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2326,47 +3182,79 @@
           <t>9/8/1/1/1/3</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="K27" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>6.9625</v>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>6.2655</v>
-      </c>
-      <c r="R27" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6.4</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>8.29</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>6.9625</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>6.2655</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>3</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2378,8 +3266,10 @@
           <t>MY WISH</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2396,47 +3286,79 @@
           <t>2/4/4/6/4/1</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K28" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>8.987500000000001</v>
-      </c>
-      <c r="P28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6.099</v>
-      </c>
-      <c r="R28" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>7.6</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>8.9875</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>6.099</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>4</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2448,8 +3370,10 @@
           <t>VOYAGE BUBBLE</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2466,47 +3390,79 @@
           <t>3/5/3/1/2/12</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="K29" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>10</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6.0508</v>
-      </c>
-      <c r="R29" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="S29" t="n">
-        <v>7.9</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>6.33</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>6.0508</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2518,8 +3474,10 @@
           <t>HELENE SUPAFEELING</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2536,47 +3494,79 @@
           <t>6/4/4/1</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K30" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>10</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.3504</v>
-      </c>
-      <c r="R30" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5.1</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>6.3504</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2588,8 +3578,10 @@
           <t>THE RED HARE</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>10</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2606,47 +3598,79 @@
           <t>3/3/2/6/3/1</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="K31" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>6</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.0669</v>
-      </c>
-      <c r="R31" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S31" t="n">
-        <v>6.7</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>7.95</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>6.0669</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>3</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2658,8 +3682,10 @@
           <t>FIT FOR BEAUTY</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>11</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2676,47 +3702,79 @@
           <t>2/1/9/6/1/2</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="K32" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.9234</v>
-      </c>
-      <c r="R32" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7.8</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5.9234</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2728,8 +3786,10 @@
           <t>ANOTHER WORLD</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>8</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2746,47 +3806,79 @@
           <t>14/8/4/5/3/1</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="K33" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>6</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.7792</v>
-      </c>
-      <c r="R33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>8.9</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6.81</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>5.7792</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2798,8 +3890,10 @@
           <t>ROMANTIC WARRIOR</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2816,47 +3910,79 @@
           <t>1/1/1/1/2/2</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="K34" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>10</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.9328</v>
-      </c>
-      <c r="R34" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.9</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>6.9328</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2868,8 +3994,10 @@
           <t>NUMBERS</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2886,47 +4014,79 @@
           <t>2/4/1/1/3</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="K35" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>6.546511627906977</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.3429</v>
-      </c>
-      <c r="R35" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.4</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>8.73</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>6.546511627906977</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>6.3429</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>3</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2938,8 +4098,10 @@
           <t>RUBYLOT</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2956,47 +4118,79 @@
           <t>12/10/10/9/5/2</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K36" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>6.441860465116279</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5.1274</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>11.6</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>6.441860465116279</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>5.1274</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3008,8 +4202,10 @@
           <t>MASQUERADE BALL</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3026,47 +4222,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4.6884</v>
-      </c>
-      <c r="R37" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="S37" t="n">
-        <v>18.1</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>4.6884</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>10</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3078,8 +4306,10 @@
           <t>LUCKY SAM GOR</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>6</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3096,47 +4326,79 @@
           <t>4/13/4/1/1/7</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="K38" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>10</v>
-      </c>
-      <c r="P38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>5.964</v>
-      </c>
-      <c r="R38" t="n">
-        <v>15</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5.7</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>5.964</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
       </c>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>10</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>2</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3148,8 +4410,10 @@
           <t>ENDUED</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>8</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3166,47 +4430,79 @@
           <t>8/2/1/3/4/6</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="K39" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>8.714285714285715</v>
-      </c>
-      <c r="P39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>5.8768</v>
-      </c>
-      <c r="R39" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S39" t="n">
-        <v>6.2</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6.48</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>8.714285714285715</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>5.8768</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
       </c>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>10</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
-        <v>3</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3218,8 +4514,10 @@
           <t>LOVERO</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>11</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3236,47 +4534,79 @@
           <t>7/3/2/1/2/11</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K40" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>7.428571428571429</v>
-      </c>
-      <c r="P40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>5.7476</v>
-      </c>
-      <c r="R40" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="S40" t="n">
-        <v>7</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7.428571428571429</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5.7476</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>10</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>4</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3288,8 +4618,10 @@
           <t>THE GOLDEN KNIGHT</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>10</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3306,47 +4638,79 @@
           <t>1/1/6/2/3/5</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="K41" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>4.214285714285714</v>
-      </c>
-      <c r="P41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5.6899</v>
-      </c>
-      <c r="R41" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="S41" t="n">
-        <v>7.5</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4.214285714285714</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5.6899</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>11</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>1</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3358,8 +4722,10 @@
           <t>SALON S</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>4</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3376,47 +4742,79 @@
           <t>1/1/1/1</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>10</v>
-      </c>
-      <c r="K42" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P42" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>6.5441</v>
-      </c>
-      <c r="R42" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5.6</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>6.5441</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>11</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>2</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3428,8 +4826,10 @@
           <t>EMBLAZON</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>14</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3446,47 +4846,79 @@
           <t>14/1/1/1/1/2</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="K43" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="L43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3.625</v>
-      </c>
-      <c r="P43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>6.2576</v>
-      </c>
-      <c r="R43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="S43" t="n">
-        <v>7.4</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9.29</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3.625</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>6.2576</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
       </c>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>11</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>3</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3498,8 +4930,10 @@
           <t>INFINITE RESOLVE</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>3</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3516,47 +4950,79 @@
           <t>6/9/2/2/1/3</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="K44" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5</v>
-      </c>
-      <c r="O44" t="n">
-        <v>4</v>
-      </c>
-      <c r="P44" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="R44" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="S44" t="n">
-        <v>8.6</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
       </c>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>11</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
-        <v>4</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3568,8 +5034,10 @@
           <t>PACKING HERMOD</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>13</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3586,39 +5054,67 @@
           <t>10/9/3/4/3/1</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="K45" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="L45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N45" t="n">
-        <v>5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>10</v>
-      </c>
-      <c r="P45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>6.1054</v>
-      </c>
-      <c r="R45" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="S45" t="n">
-        <v>8.6</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6.1054</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
       </c>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3797,7 +5293,6 @@
           <t>6/4/4/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.4</v>
       </c>
@@ -3878,7 +5373,6 @@
           <t>3/3/2/6/3/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.95</v>
       </c>
@@ -3959,7 +5453,6 @@
           <t>2/1/9/6/1/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.38</v>
       </c>
@@ -4040,7 +5533,6 @@
           <t>14/8/4/5/3/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.81</v>
       </c>
@@ -4121,7 +5613,6 @@
           <t>1/1/2/6/6/3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.71</v>
       </c>
@@ -4202,7 +5693,6 @@
           <t>8/3/4/1/9/3</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>6.38</v>
       </c>
@@ -4283,7 +5773,6 @@
           <t>6/9/6/1/1/3</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>7.52</v>
       </c>
@@ -4364,7 +5853,6 @@
           <t>8/1/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.67</v>
       </c>
@@ -4445,7 +5933,6 @@
           <t>4/5/3/5/5/4</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5.76</v>
       </c>
@@ -4526,7 +6013,6 @@
           <t>7/3/10/9/5/2</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5.19</v>
       </c>
@@ -4607,7 +6093,6 @@
           <t>14/12/4/13/8/4</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>3.38</v>
       </c>
@@ -4688,7 +6173,6 @@
           <t>8/8/12/9/7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.13</v>
       </c>
@@ -4769,7 +6253,6 @@
           <t>13/12</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1</v>
       </c>
@@ -4850,7 +6333,6 @@
           <t>8/9/14/12/14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1.2</v>
       </c>
@@ -5062,7 +6544,6 @@
           <t>1/1/1/1/2/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9.48</v>
       </c>
@@ -5143,7 +6624,6 @@
           <t>2/4/1/1/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>8.73</v>
       </c>
@@ -5224,7 +6704,6 @@
           <t>12/10/10/9/5/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.43</v>
       </c>
@@ -5305,7 +6784,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -5386,7 +6864,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -5467,7 +6944,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -5548,7 +7024,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -5629,7 +7104,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
@@ -5841,7 +7315,6 @@
           <t>4/13/4/1/1/7</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.38</v>
       </c>
@@ -5922,7 +7395,6 @@
           <t>8/2/1/3/4/6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.48</v>
       </c>
@@ -6003,7 +7475,6 @@
           <t>7/3/2/1/2/11</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.52</v>
       </c>
@@ -6084,7 +7555,6 @@
           <t>1/1/6/2/3/5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>7.05</v>
       </c>
@@ -6165,7 +7635,6 @@
           <t>8/12/1/3/5/6</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.48</v>
       </c>
@@ -6246,7 +7715,6 @@
           <t>4/5/8/9/1/5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.24</v>
       </c>
@@ -6327,7 +7795,6 @@
           <t>10/4/9/5/10/4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.81</v>
       </c>
@@ -6408,7 +7875,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
@@ -6489,7 +7955,6 @@
           <t>1/7/6/5/6/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.38</v>
       </c>
@@ -6570,7 +8035,6 @@
           <t>7/12/10/12/5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.47</v>
       </c>
@@ -6651,7 +8115,6 @@
           <t>10/11/5/3/12/14</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.9</v>
       </c>
@@ -6732,7 +8195,6 @@
           <t>6/14/11/14/10/14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.14</v>
       </c>
@@ -6813,7 +8275,6 @@
           <t>10/8</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1.67</v>
       </c>
@@ -6894,7 +8355,6 @@
           <t>12/2/4/12/13/14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2.48</v>
       </c>
@@ -7106,7 +8566,6 @@
           <t>1/1/1/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>10</v>
       </c>
@@ -7272,7 +8731,6 @@
           <t>6/9/2/2/1/3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>8.050000000000001</v>
       </c>
@@ -7353,7 +8811,6 @@
           <t>10/9/3/4/3/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>7.29</v>
       </c>
@@ -7434,7 +8891,6 @@
           <t>3/2/4/2/1/4</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>7.9</v>
       </c>
@@ -7515,7 +8971,6 @@
           <t>13/5/7/7/1/1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>6.76</v>
       </c>
@@ -7596,7 +9051,6 @@
           <t>2/1/1/1/8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>7.27</v>
       </c>
@@ -7677,7 +9131,6 @@
           <t>4/9/3/8/8/1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5.33</v>
       </c>
@@ -7758,7 +9211,6 @@
           <t>1/2/6/6/2</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>6.73</v>
       </c>
@@ -7839,7 +9291,6 @@
           <t>5/13/4/2/10/2</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5.71</v>
       </c>
@@ -7920,7 +9371,6 @@
           <t>8/2/3/3/5/7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>5.67</v>
       </c>
@@ -8001,7 +9451,6 @@
           <t>1/11/3/10/8/10</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.67</v>
       </c>
@@ -8082,7 +9531,6 @@
           <t>8/7/12/1/10/12</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.95</v>
       </c>
@@ -8163,7 +9611,6 @@
           <t>1/12/7/6/8/4</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>3.95</v>
       </c>
@@ -8348,7 +9795,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>11</t>
@@ -8450,7 +9896,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>1</t>
@@ -8552,7 +9997,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>2</t>
@@ -8654,7 +10098,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>4</t>
@@ -8756,7 +10199,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>1</t>
@@ -8858,7 +10300,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>5</t>
@@ -8960,7 +10401,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>10</t>
@@ -9062,7 +10502,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
@@ -9164,7 +10603,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>2</t>
@@ -9266,7 +10704,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>1</t>
@@ -9368,7 +10805,6 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>11</t>
@@ -9643,7 +11079,6 @@
           <t>6/2/2/2/6/4</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.71</v>
       </c>
@@ -9724,7 +11159,6 @@
           <t>3/2/3/3/8/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.1</v>
       </c>
@@ -9805,7 +11239,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -9886,7 +11319,6 @@
           <t>6/12/5/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>3.7</v>
       </c>
@@ -9967,7 +11399,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -10048,7 +11479,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -10129,7 +11559,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -10210,7 +11639,6 @@
           <t>9/3/13/8/8/4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.57</v>
       </c>
@@ -10291,7 +11719,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5</v>
       </c>
@@ -10372,7 +11799,6 @@
           <t>14/6/12/12/8/1</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>4.1</v>
       </c>
@@ -10453,7 +11879,6 @@
           <t>6/9/5/10/9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.47</v>
       </c>
@@ -10534,7 +11959,6 @@
           <t>9/8/6</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>3</v>
       </c>
@@ -10615,7 +12039,6 @@
           <t>11/11/9/6</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.5</v>
       </c>
@@ -10696,7 +12119,6 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1</v>
       </c>
@@ -10908,7 +12330,6 @@
           <t>9/-/1/2/2/6</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.62</v>
       </c>
@@ -10989,7 +12410,6 @@
           <t>1/4/3/4/5/9</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.1</v>
       </c>
@@ -11070,7 +12490,6 @@
           <t>4/4/2/7/7/4</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.14</v>
       </c>
@@ -11151,7 +12570,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -11232,7 +12650,6 @@
           <t>5/11/3/10/5/3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.14</v>
       </c>
@@ -11313,7 +12730,6 @@
           <t>10/5/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.83</v>
       </c>
@@ -11394,7 +12810,6 @@
           <t>8/4/6/9/8/7</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.95</v>
       </c>
@@ -11475,7 +12890,6 @@
           <t>3/6/5/8/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.93</v>
       </c>
@@ -11556,7 +12970,6 @@
           <t>2/9/10/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.2</v>
       </c>
@@ -11637,7 +13050,6 @@
           <t>11/11/14/2/9/5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.9</v>
       </c>
@@ -11718,7 +13130,6 @@
           <t>5/8/7/12/12/14</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.57</v>
       </c>
@@ -11799,7 +13210,6 @@
           <t>7/13/9/13/14/13</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.24</v>
       </c>
@@ -11880,7 +13290,6 @@
           <t>10/7/11/6/7/9</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.52</v>
       </c>
@@ -11961,7 +13370,6 @@
           <t>7/4/9/7/11/10</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2.1</v>
       </c>
@@ -12173,7 +13581,6 @@
           <t>6/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8</v>
       </c>
@@ -12254,7 +13661,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5</v>
       </c>
@@ -12335,7 +13741,6 @@
           <t>12/5/6/11/4/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.29</v>
       </c>
@@ -12416,7 +13821,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -12497,7 +13901,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -12578,7 +13981,6 @@
           <t>13/6/14/4/1/8</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.67</v>
       </c>
@@ -12659,7 +14061,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -12740,7 +14141,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
@@ -12821,7 +14221,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5</v>
       </c>
@@ -12902,7 +14301,6 @@
           <t>8/3/3/6/7/9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>4.05</v>
       </c>
@@ -12983,7 +14381,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>5</v>
       </c>
@@ -13064,7 +14461,6 @@
           <t>6/5/3/7/9/9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>3.43</v>
       </c>
@@ -13145,7 +14541,6 @@
           <t>1/4/4/12/4/5</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>4.95</v>
       </c>
@@ -13442,7 +14837,6 @@
           <t>4/10/4/3/5/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.81</v>
       </c>
@@ -13523,7 +14917,6 @@
           <t>2/5/2/1/8/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.29</v>
       </c>
@@ -13604,7 +14997,6 @@
           <t>11/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.33</v>
       </c>
@@ -13685,7 +15077,6 @@
           <t>5/1/6/3/5/5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.9</v>
       </c>
@@ -13766,7 +15157,6 @@
           <t>1/6/1/6/12/5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.71</v>
       </c>
@@ -13847,7 +15237,6 @@
           <t>10/6/8/3/5/2</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>6</v>
       </c>
@@ -13928,7 +15317,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -14009,7 +15397,6 @@
           <t>8/4/4/5/10/7</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.57</v>
       </c>
@@ -14090,7 +15477,6 @@
           <t>9/4</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.67</v>
       </c>
@@ -14171,7 +15557,6 @@
           <t>7/9/7/8/5/3</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>4.62</v>
       </c>
@@ -14252,7 +15637,6 @@
           <t>12/5/2/3/4/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>5.05</v>
       </c>
@@ -14333,7 +15717,6 @@
           <t>9/6</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>3.33</v>
       </c>
@@ -14414,7 +15797,6 @@
           <t>1/8/6/4/10/5</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>4.05</v>
       </c>
@@ -14495,7 +15877,6 @@
           <t>12/12/10/8</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1.4</v>
       </c>
@@ -14707,7 +16088,6 @@
           <t>1/1/1/1/1/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>10</v>
       </c>
@@ -14788,7 +16168,6 @@
           <t>5/1/3/3/2/6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.14</v>
       </c>
@@ -14869,7 +16248,6 @@
           <t>2/2/2/5/3/5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.86</v>
       </c>
@@ -14950,7 +16328,6 @@
           <t>3/5/4/2/5/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>7.19</v>
       </c>
@@ -15031,7 +16408,6 @@
           <t>9/2/3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>7.33</v>
       </c>
@@ -15112,7 +16488,6 @@
           <t>6/4/6/5/5/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.62</v>
       </c>
@@ -15193,7 +16568,6 @@
           <t>5/10/1/7/7/10</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.33</v>
       </c>
@@ -15274,7 +16648,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
@@ -15486,7 +16859,6 @@
           <t>4/1/1/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9.07</v>
       </c>
@@ -15567,7 +16939,6 @@
           <t>2/3/5/6/1/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.62</v>
       </c>
@@ -15648,7 +17019,6 @@
           <t>6/2/3/3/4/9</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.71</v>
       </c>
@@ -15729,7 +17099,6 @@
           <t>8/4/4/3/6/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.14</v>
       </c>
@@ -15810,7 +17179,6 @@
           <t>6/4/7/1/4/6</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.67</v>
       </c>
@@ -15891,7 +17259,6 @@
           <t>9/12/7/10/6/3</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.05</v>
       </c>
@@ -15972,7 +17339,6 @@
           <t>9/7/3/10/1/7</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.95</v>
       </c>
@@ -16138,7 +17504,6 @@
           <t>11/6/6/1/12/4</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.86</v>
       </c>
@@ -16219,7 +17584,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5</v>
       </c>
@@ -16385,7 +17749,6 @@
           <t>9/6/7/11/11/5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.76</v>
       </c>
@@ -16466,7 +17829,6 @@
           <t>14/6/11/5/8/12</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.29</v>
       </c>
@@ -16547,7 +17909,6 @@
           <t>3/6/14/12/12</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1.87</v>
       </c>
@@ -16759,7 +18120,6 @@
           <t>1/2/6/1/1/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9.050000000000001</v>
       </c>
@@ -16840,7 +18200,6 @@
           <t>9/8/1/1/1/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>8.289999999999999</v>
       </c>
@@ -16921,7 +18280,6 @@
           <t>2/4/4/6/4/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.9</v>
       </c>
@@ -17002,7 +18360,6 @@
           <t>3/5/3/1/2/12</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.33</v>
       </c>
@@ -17083,7 +18440,6 @@
           <t>4/4/7/5/1/6</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.76</v>
       </c>
@@ -17164,7 +18520,6 @@
           <t>1/3/2/4/4/11</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.38</v>
       </c>
@@ -17245,7 +18600,6 @@
           <t>7/-/8/2/3/5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5.57</v>
       </c>
@@ -17326,7 +18680,6 @@
           <t>6/14/6/2/2/8</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5.29</v>
       </c>
@@ -17407,7 +18760,6 @@
           <t>8/7/4/13/2/4</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5.29</v>
       </c>
@@ -17488,7 +18840,6 @@
           <t>14/9/9/3/12/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.57</v>
       </c>
@@ -17569,7 +18920,6 @@
           <t>6/5/7/6/7/12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.86</v>
       </c>
@@ -17650,7 +19000,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>5</v>
       </c>
@@ -17731,7 +19080,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>5</v>
       </c>
@@ -17812,7 +19160,6 @@
           <t>4/12</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2.67</v>
       </c>
